--- a/fixtures/manual-check/metrics.xlsx
+++ b/fixtures/manual-check/metrics.xlsx
@@ -6,7 +6,7 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <x:sheet name="Sales Metrics" sheetId="1" r:id="rId2"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -14,44 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Region</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quarter</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Amount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Total:</x:t>
-  </x:si>
-  <x:si>
-    <x:t>North</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>South</x:t>
-  </x:si>
-  <x:si>
-    <x:t>East</x:t>
-  </x:si>
-  <x:si>
-    <x:t>West</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Q2</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="0" formatCode=""/>
+    <x:numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </x:numFmts>
   <x:fonts count="1">
     <x:font>
@@ -89,10 +59,11 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1"/>
   </x:cellStyleXfs>
   <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -100,22 +71,11 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
-  <x:cellStyles count="1">
+  <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <x:cellStyle name="Currency-Red" xfId="1"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Sales" displayName="Sales" ref="A1:C7" totalsRowCount="1">
-  <x:autoFilter ref="A1:C6"/>
-  <x:tableColumns count="3">
-    <x:tableColumn id="1" name="Region"/>
-    <x:tableColumn id="2" name="Quarter"/>
-    <x:tableColumn id="3" name="Amount" totalsRowFunction="sum"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -407,94 +367,12 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15" outlineLevelCol="1"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:6">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E1" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F1" s="0">
-        <x:f>SUM(Sales[Amount])</x:f>
-        <x:v>965</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" hidden="1" outlineLevel="1" collapsed="1">
-      <x:c r="A2" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="0">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6" hidden="1" outlineLevel="1" collapsed="1">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="0">
-        <x:v>250</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6" hidden="1" outlineLevel="1" collapsed="1">
-      <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="0">
-        <x:v>175</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6" hidden="1" outlineLevel="1" collapsed="1">
-      <x:c r="A5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="0">
-        <x:v>300</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6" hidden="1" outlineLevel="1" collapsed="1">
-      <x:c r="A6" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="0">
-        <x:v>140</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6">
-      <x:c r="C7" s="0">
-        <x:f>SUBTOTAL(109,[Amount])</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
-  <x:tableParts count="1">
-    <x:tablePart r:id="rId5"/>
-  </x:tableParts>
+  <x:tableParts count="0"/>
 </x:worksheet>
 </file>